--- a/public/templates/test_input/Input_bao_cao_18.xlsx
+++ b/public/templates/test_input/Input_bao_cao_18.xlsx
@@ -759,67 +759,65 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ca 3</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>PX Khai thác 2</t>
+          <t>PX Khai thác 3</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Trần Văn B</t>
+          <t>Nguyễn Văn A</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>164</v>
+        <v>316</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" s="28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K4" s="28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L4" s="28" t="n">
         <v>2.1</v>
       </c>
-      <c r="J4" s="28" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K4" s="28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L4" s="28" t="n">
-        <v>2.8</v>
-      </c>
       <c r="M4" s="28" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>7.9</v>
+        <v>4.6</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="P4" s="28" t="n">
-        <v>17</v>
+        <v>11.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="12" t="inlineStr">
         <is>
-          <t>Máy khoan gặp sự cố, tiến độ chậm.</t>
+          <t>Điều kiện sản xuất ổn định.</t>
         </is>
       </c>
     </row>
